--- a/pc-fixe/pc-gaming-occasion.xlsx
+++ b/pc-fixe/pc-gaming-occasion.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2495,6 +2495,438 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- Recherche du 03/06 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5500 + RTX 3060 12Go + B450 Tomahawk Max II + beQuiet 600W</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>500 € (↓ −49€ était 549€)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>↓ −49€</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5500 (6C/12T Zen 3, PCIe 3.0 limité)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RTX 3060 12 Go</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>+50-60% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MSI B450 Tomahawk Max II ✅</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>B450 (acceptable, PCIe 3.0)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 3200 MHz (dual channel non confirmé)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>be quiet! 600W 80+ Bronze ✅</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SQ-Tower vitre trempée (ATX ? — à confirmer)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Jouy-le-Moutier (95) — Val-d'Oise, IDF</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Très bon état</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non précisé (0 avis ⚠️)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>RTX 3060 12 Go excellent pour 1440p. B450 Tomahawk Max II = une des meilleures B450. be quiet! 600W Bronze. Ryzen 5 5500 Zen 3. Prix baissé de 549€. IDF.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0 avis vendeur (risque). Boîtier 'SQ-Tower' = marque inconnue (confirmer ATX standard). Ryzen 5500 = PCIe 3.0 seulement. Dual channel non confirmé. Pas de livraison.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3206242421</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ryzen 7 2700X + RTX 3060 12Go + B450 Aorus — Alim inconnue</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>500 €</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f> Stable</f>
+        <v/>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ryzen 7 2700X (8C/16T Zen+, 2018)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RTX 3060 12 Go</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>+50-60% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Gigabyte Aorus B450 ✅</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B450 (acceptable)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 (fréq. inconnue ⚠️)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>SSD 500 Go + HDD 2 To ✅</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Non précisée ⚠️ CRITIQUE</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Be Quiet! (ATX probable ✅)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Romorantin-Lanthenay (41) — Centre, province éloignée</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Très bon état (2020)</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1/1 (13 avis) ✅</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>RTX 3060 12 Go excellent. B450 Aorus bonne CM. Be Quiet boîtier ATX. 2,5 To stockage. Bon vendeur.</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Alim non précisée (CRITIQUE — demander impérativement). Ryzen 7 2700X = Zen+ 2018 (vieux, inférieur au 3600 en single-core). RAM fréquence inconnue. Province éloignée. Pas de livraison.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3209364742</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RTX 2070 Super + Ryzen 5 3600 + A520M + 650W CM Bronze — CHIPSET DISQUALIFIÉ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>470 € (ferme)</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f> Stable</f>
+        <v/>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ryzen 5 3600 (6C/12T Zen 2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>EVGA RTX 2070 Super 8 Go</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>+35-45% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Gigabyte A520M-K V2 ❌</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>A520 ❌ (liste noire : bas de gamme, pas d'OC)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 dual channel 2×8 ✅ (fréq. inconnue)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>SSD NVMe 512 Go</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Cooler Master 650W 80+ Bronze ✅</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Xigmatek Alphard M (ATX présumé)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Conflans-Sainte-Honorine (78) — Ile-de-France</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>État neuf</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0.96/1 (57 avis) ✅✅</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>RTX 2070 Super = excellent GPU. PSU 650W Bronze Cooler Master ✅. Dual channel. Vendeur très fiable (57 avis). Revendeur pro assemblant des PCs.</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>❌ Chipset A520 DISQUALIFIÉ (liste noire). Ryzen 5 3600 Zen 2. Pas de livraison. Prix ferme.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3206371043</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RTX 2070 Super + Ryzen 5 3500X + A520M + 650W CM Bronze — CHIPSET DISQUALIFIÉ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>470 €</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f> Stable</f>
+        <v/>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ryzen 5 3500X (6C/6T Zen 2, sans HT)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MSI RTX 2070 Super Ventus 2X 8 Go</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>+35-45% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Gigabyte A520M-K V2 ❌</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>A520 ❌ (liste noire : bas de gamme, pas d'OC)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 dual channel 2×8 ✅ (fréq. inconnue)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>SSD NVMe 512 Go Micron</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Cooler Master 650W 80+ Bronze ✅</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Aerocool P500B (ATX présumé)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Conflans-Sainte-Honorine (78) — Ile-de-France</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>État neuf</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>0.98/1 (112 avis) ✅✅✅</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>RTX 2070 Super = excellent GPU. PSU 650W Bronze Cooler Master ✅. Dual channel. Vendeur ultra-fiable (112 avis). Watercooling + affichage digital.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>❌ Chipset A520 DISQUALIFIÉ (liste noire). Ryzen 5 3500X = 6C sans hyperthreading. Pas de livraison. Même vendeur pro que ID 3206371043.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3207350642</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2507,7 +2939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2670,6 +3102,57 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>--- Recherche du 03/06 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>🥇 MEILLEUR NOUVEAU DEAL — Ryzen 5 5500 + RTX 3060 12Go + B450 Tomahawk @ 500€</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ — ID: 3206242421 | Jouy-le-Moutier (95)
+RTX 3060 12 Go + MSI B450 Tomahawk Max II + beQuiet 600W Bronze. Prix baissé de 549€.
+⚠️ 0 avis vendeur — à contacter prudemment. Demander : dual channel RAM + ATX boîtier.
+→ https://www.leboncoin.fr/ad/ordinateurs/3206242421</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2️⃣ À INVESTIGUER — Ryzen 7 2700X + RTX 3060 12Go + B450 Aorus @ 500€</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ — ID: 3209364742 | Romorantin-Lanthenay (41)
+RTX 3060 12 Go + B450 Aorus. HDD 2 To + SSD 500 Go. Bon vendeur (13 avis).
+⚠️ DEMANDER IMPÉRATIVEMENT : marque + wattage alim.
+→ https://www.leboncoin.fr/ad/ordinateurs/3209364742</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>⚠️ RTX 2070 Super disqualifiés (A520) — à éviter ou négocier fort</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>⭐⭐ — IDs: 3206371043 (3600) et 3207350642 (3500X) @ 470€ | Conflans (78)
+GPU excellent mais A520 sur liste noire. Même revendeur pro. PSU 650W Bronze ✅.
+Si alim/boîtier remplaçables et deal à 400€ → reconsidérer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
